--- a/static/data/exports/Retro_AS_AE_2016.xlsx
+++ b/static/data/exports/Retro_AS_AE_2016.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_AS_AE_2016.xlsx
+++ b/static/data/exports/Retro_AS_AE_2016.xlsx
@@ -1656,11 +1656,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E20" t="n">
         <v>1638</v>
@@ -9034,11 +9034,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E139" t="n">
         <v>1961</v>
@@ -10513,20 +10513,20 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1721769</v>
+        <v>1721770</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Jawahar Lal Goala</t>
+          <t>Manindra Chandra Das</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>19861</v>
+        <v>19886</v>
       </c>
       <c r="E163" t="n">
         <v>401</v>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Jawahar Lal Goala</t>
+          <t>Manindra Chandra Das</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="Q163" t="b">
@@ -10575,20 +10575,20 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1721770</v>
+        <v>1721769</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Manindra Chandra Das</t>
+          <t>Jawahar Lal Goala</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>19886</v>
+        <v>19861</v>
       </c>
       <c r="E164" t="n">
         <v>401</v>
@@ -10612,12 +10612,12 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Manindra Chandra Das</t>
+          <t>Jawahar Lal Goala</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q164" t="b">
@@ -12258,11 +12258,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E191" t="n">
         <v>2438</v>
@@ -16474,11 +16474,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E259" t="n">
         <v>669</v>
@@ -22302,11 +22302,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E353" t="n">
         <v>5991</v>
@@ -22798,11 +22798,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E361" t="n">
         <v>3315</v>
@@ -26580,11 +26580,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E422" t="n">
         <v>29082</v>
@@ -29432,11 +29432,11 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E468" t="n">
         <v>1976</v>
@@ -30548,11 +30548,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E486" t="n">
         <v>3626</v>
@@ -33462,11 +33462,11 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E533" t="n">
         <v>1944</v>
@@ -37864,11 +37864,11 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D604" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E604" t="n">
         <v>12261</v>
@@ -39228,11 +39228,11 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D626" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E626" t="n">
         <v>1676</v>
@@ -47722,11 +47722,11 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D763" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E763" t="n">
         <v>8033</v>
@@ -48342,11 +48342,11 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D773" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E773" t="n">
         <v>4914</v>
@@ -59006,11 +59006,11 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D945" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E945" t="n">
         <v>1548</v>
@@ -66384,11 +66384,11 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1064" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1064" t="n">
         <v>2270</v>
@@ -67004,11 +67004,11 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1074" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1074" t="n">
         <v>3830</v>
@@ -70724,11 +70724,11 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1134" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1134" t="n">
         <v>4026</v>
@@ -73824,11 +73824,11 @@
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1184" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1184" t="n">
         <v>2310</v>
